--- a/artfynd/A 58837-2025 artfynd.xlsx
+++ b/artfynd/A 58837-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -913,6 +913,225 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>129923383</v>
+      </c>
+      <c r="B4" t="n">
+        <v>91201</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>3086</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Svartöra</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Auricularia mesenterica</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Dicks.:Fr.) Pers.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Barnmossen, Barnmossen, Nrk</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>507275</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6572338</v>
+      </c>
+      <c r="S4" t="n">
+        <v>15</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>09:28</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>09:28</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På ett antal utslängda almstockar.</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Erik Göthlin</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Erik Göthlin</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>129923392</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58106</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Barnmossen, Barnmossen, Nrk</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>507275</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6572338</v>
+      </c>
+      <c r="S5" t="n">
+        <v>15</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>09:28</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>09:28</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Erik Göthlin</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Erik Göthlin</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 58837-2025 artfynd.xlsx
+++ b/artfynd/A 58837-2025 artfynd.xlsx
@@ -918,7 +918,7 @@
         <v>129923383</v>
       </c>
       <c r="B4" t="n">
-        <v>91201</v>
+        <v>91204</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>129923392</v>
       </c>
       <c r="B5" t="n">
-        <v>58106</v>
+        <v>58108</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 58837-2025 artfynd.xlsx
+++ b/artfynd/A 58837-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -918,7 +918,7 @@
         <v>129923383</v>
       </c>
       <c r="B4" t="n">
-        <v>91204</v>
+        <v>91207</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>129923392</v>
       </c>
       <c r="B5" t="n">
-        <v>58108</v>
+        <v>58111</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,6 +1131,112 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>130008416</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57896</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>103020</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Entita</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Poecile palustris</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Karlslundsåsen, Karlslundsåsen, Nrk</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>507357</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6572709</v>
+      </c>
+      <c r="S6" t="n">
+        <v>20</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Erik Göthlin</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Erik Göthlin</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 58837-2025 artfynd.xlsx
+++ b/artfynd/A 58837-2025 artfynd.xlsx
@@ -918,7 +918,7 @@
         <v>129923383</v>
       </c>
       <c r="B4" t="n">
-        <v>91207</v>
+        <v>91208</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 58837-2025 artfynd.xlsx
+++ b/artfynd/A 58837-2025 artfynd.xlsx
@@ -918,7 +918,7 @@
         <v>129923383</v>
       </c>
       <c r="B4" t="n">
-        <v>91208</v>
+        <v>91225</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>129923392</v>
       </c>
       <c r="B5" t="n">
-        <v>58111</v>
+        <v>58112</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1137,7 +1137,7 @@
         <v>130008416</v>
       </c>
       <c r="B6" t="n">
-        <v>57896</v>
+        <v>57897</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 58837-2025 artfynd.xlsx
+++ b/artfynd/A 58837-2025 artfynd.xlsx
@@ -918,7 +918,7 @@
         <v>129923383</v>
       </c>
       <c r="B4" t="n">
-        <v>91241</v>
+        <v>91243</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 58837-2025 artfynd.xlsx
+++ b/artfynd/A 58837-2025 artfynd.xlsx
@@ -918,7 +918,7 @@
         <v>129923383</v>
       </c>
       <c r="B4" t="n">
-        <v>91243</v>
+        <v>91330</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>129923392</v>
       </c>
       <c r="B5" t="n">
-        <v>58113</v>
+        <v>58198</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1137,7 +1137,7 @@
         <v>130008416</v>
       </c>
       <c r="B6" t="n">
-        <v>57898</v>
+        <v>57983</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 58837-2025 artfynd.xlsx
+++ b/artfynd/A 58837-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>105889757</v>
+        <v>105889722</v>
       </c>
       <c r="B2" t="n">
-        <v>89014</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91502</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -722,10 +717,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>507278.5151873111</v>
+        <v>507285</v>
       </c>
       <c r="R2" t="n">
-        <v>6572356.102379088</v>
+        <v>6572337</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -757,7 +752,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -767,7 +762,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -795,15 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>105889722</v>
+        <v>129923383</v>
       </c>
       <c r="B3" t="n">
-        <v>89014</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91502</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -829,26 +819,19 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Karlslunds motionsspår, Nrk</t>
+          <t>Barnmossen, Barnmossen, Nrk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>507284.6925189525</v>
+        <v>507275</v>
       </c>
       <c r="R3" t="n">
-        <v>6572337.212391006</v>
+        <v>6572338</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -872,22 +855,27 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-01-09</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-01-09</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:28</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På ett antal utslängda almstockar.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -896,29 +884,28 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Barbro Fehrm Friberg</t>
+          <t>Erik Göthlin</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Barbro Fehrm Friberg</t>
+          <t>Erik Göthlin</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129923383</v>
+        <v>91805799</v>
       </c>
       <c r="B4" t="n">
-        <v>91330</v>
+        <v>91930</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -926,37 +913,48 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3086</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svartöra</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Auricularia mesenterica</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Dicks.:Fr.) Pers.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Barnmossen, Barnmossen, Nrk</t>
+          <t>Södra Runnaby, Nrk</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>507275</v>
+        <v>507293</v>
       </c>
       <c r="R4" t="n">
-        <v>6572338</v>
+        <v>6572696</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -980,27 +978,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>09:28</t>
+          <t>2021-03-23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>09:28</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På ett antal utslängda almstockar.</t>
+          <t>2021-03-23</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1009,66 +992,88 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>Gammalt levande träd med bohål.</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Gammalt levande träd med bohål.</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Erik Göthlin</t>
+          <t>Barbro Fehrm Friberg</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Erik Göthlin</t>
+          <t>Barbro Fehrm Friberg</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129923392</v>
+        <v>113403648</v>
       </c>
       <c r="B5" t="n">
-        <v>58198</v>
+        <v>91930</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>5442</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Barnmossen, Barnmossen, Nrk</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>507275</v>
+        <v>507290</v>
       </c>
       <c r="R5" t="n">
-        <v>6572338</v>
+        <v>6572687</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1092,22 +1097,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>09:28</t>
+          <t>2023-11-25</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>09:28</t>
+          <t>2023-11-25</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1134,10 +1129,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130008416</v>
+        <v>112003503</v>
       </c>
       <c r="B6" t="n">
-        <v>57983</v>
+        <v>93235</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1145,46 +1140,40 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103020</v>
+        <v>5966</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Karlslundsåsen, Karlslundsåsen, Nrk</t>
+          <t>Södra Runnaby, Nrk</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>507357</v>
+        <v>507293</v>
       </c>
       <c r="R6" t="n">
-        <v>6572709</v>
+        <v>6572696</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1208,12 +1197,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2023-09-10</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2023-09-10</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1222,21 +1211,461 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
+          <t>Barbro Fehrm Friberg</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Barbro Fehrm Friberg, Lotta Sörman, Ankie Rauséus</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>92222386</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57903</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>102110</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Fjällvråk</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Buteo lagopus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Pontoppidan, 1763)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Södra Runnaby, Nrk</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>507293</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6572696</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2021-04-06</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>14:19</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2021-04-06</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>14:19</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Barbro Fehrm Friberg</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Barbro Fehrm Friberg</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>129923392</v>
+      </c>
+      <c r="B8" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Barnmossen, Barnmossen, Nrk</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>507275</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6572338</v>
+      </c>
+      <c r="S8" t="n">
+        <v>15</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>09:28</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>09:28</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
           <t>Erik Göthlin</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
+      <c r="AX8" t="inlineStr">
         <is>
           <t>Erik Göthlin</t>
         </is>
       </c>
-      <c r="AY6" t="inlineStr"/>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>130008416</v>
+      </c>
+      <c r="B9" t="n">
+        <v>58112</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>103020</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Entita</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Poecile palustris</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Karlslundsåsen, Karlslundsåsen, Nrk</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>507357</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6572709</v>
+      </c>
+      <c r="S9" t="n">
+        <v>20</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Erik Göthlin</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Erik Göthlin</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>129923394</v>
+      </c>
+      <c r="B10" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>V Barnmossen, V Barnmossen, Nrk</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>507251</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6572371</v>
+      </c>
+      <c r="S10" t="n">
+        <v>15</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>09:28</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>09:28</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Erik Göthlin</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Erik Göthlin</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 58837-2025 artfynd.xlsx
+++ b/artfynd/A 58837-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -787,6 +792,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105889722</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -899,6 +909,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129923383</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1028,6 +1043,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91805799</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1126,6 +1146,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113403648</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1227,6 +1252,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112003503</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1346,6 +1376,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92222386</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1453,6 +1488,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129923392</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1559,6 +1599,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130008416</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1666,8 +1711,24 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129923394</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>